--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T15:34:05+00:00</t>
+    <t>2026-01-20T16:02:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T16:02:03+00:00</t>
+    <t>2026-01-20T17:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T17:55:30+00:00</t>
+    <t>2026-01-21T09:01:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T09:01:08+00:00</t>
+    <t>2026-01-21T09:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T09:55:17+00:00</t>
+    <t>2026-01-21T13:58:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T13:58:49+00:00</t>
+    <t>2026-01-21T14:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T14:06:50+00:00</t>
+    <t>2026-01-21T14:35:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T14:35:59+00:00</t>
+    <t>2026-01-23T08:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T08:59:40+00:00</t>
+    <t>2026-02-03T08:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T08:21:15+00:00</t>
+    <t>2026-02-03T10:50:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:50:43+00:00</t>
+    <t>2026-02-03T13:25:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T13:25:15+00:00</t>
+    <t>2026-02-04T07:54:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T07:54:35+00:00</t>
+    <t>2026-02-04T09:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T09:29:46+00:00</t>
+    <t>2026-02-04T11:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T11:22:34+00:00</t>
+    <t>2026-02-05T10:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T10:48:12+00:00</t>
+    <t>2026-02-05T13:45:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T13:45:20+00:00</t>
+    <t>2026-02-05T14:33:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T14:33:14+00:00</t>
+    <t>2026-02-06T15:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T15:11:45+00:00</t>
+    <t>2026-02-09T15:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T15:38:00+00:00</t>
+    <t>2026-02-10T14:06:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T14:06:03+00:00</t>
+    <t>2026-02-11T08:41:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T08:41:28+00:00</t>
+    <t>2026-02-11T08:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T08:47:58+00:00</t>
+    <t>2026-02-12T14:05:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:05:06+00:00</t>
+    <t>2026-02-13T15:05:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:05:24+00:00</t>
+    <t>2026-02-13T16:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T16:24:26+00:00</t>
+    <t>2026-02-13T16:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T16:45:56+00:00</t>
+    <t>2026-02-17T08:37:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:34:27+00:00</t>
+    <t>2026-02-23T15:50:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:50:03+00:00</t>
+    <t>2026-02-24T10:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:01:10+00:00</t>
+    <t>2026-02-25T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T15:11:58+00:00</t>
+    <t>2026-02-26T09:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T09:34:21+00:00</t>
+    <t>2026-02-27T08:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T08:28:09+00:00</t>
+    <t>2026-02-27T09:24:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T09:24:41+00:00</t>
+    <t>2026-02-27T09:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T09:26:51+00:00</t>
+    <t>2026-02-27T09:31:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T09:31:51+00:00</t>
+    <t>2026-02-27T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:14:27+00:00</t>
+    <t>2026-03-02T14:14:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T14:14:24+00:00</t>
+    <t>2026-03-10T12:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T12:57:18+00:00</t>
+    <t>2026-03-10T13:12:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T13:12:33+00:00</t>
+    <t>2026-03-18T14:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T14:29:18+00:00</t>
+    <t>2026-03-19T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T08:56:44+00:00</t>
+    <t>2026-03-23T13:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
+++ b/sfe-lot-3-serafin/ig/CodeSystem-input-tddui-task-transport-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:01:42+00:00</t>
+    <t>2026-03-24T16:53:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
